--- a/Assets/Samples/TGADemo/Excels/Networks/Cmds/NetworkCmds.xlsx
+++ b/Assets/Samples/TGADemo/Excels/Networks/Cmds/NetworkCmds.xlsx
@@ -1134,7 +1134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U7"/>
+  <dimension ref="A1:U8"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="13" defaultRowHeight="16.8"/>
   <cols>
     <col width="12" customWidth="1" style="1" min="1" max="1"/>
@@ -1392,7 +1392,33 @@
       <c r="T7" s="7" t="n"/>
       <c r="U7" s="7" t="n"/>
     </row>
-    <row r="8" ht="22" customHeight="1"/>
+    <row r="8" ht="22" customHeight="1">
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>AppCustomConfig</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>拉取GM后台应用配置URL</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>HTTP_POST</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>GameServer</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>/v1/common/app-config</t>
+        </is>
+      </c>
+    </row>
     <row r="9" ht="22" customHeight="1"/>
     <row r="10" ht="22" customHeight="1"/>
     <row r="11" ht="22" customHeight="1"/>
